--- a/Danh muc.xlsx
+++ b/Danh muc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Vandonstay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C54E3FB4-BB30-4433-B838-9AED8FD93B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51053DE3-E374-4CFC-8BEB-A7C0A164CAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -287,7 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -300,19 +300,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+      <alignment vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -599,337 +604,337 @@
   <cols>
     <col min="1" max="2" width="9.140625" style="2"/>
     <col min="3" max="3" width="38.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="B8" s="9">
         <v>6</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="B9" s="9">
         <v>7</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>8</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <v>9</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
+      <c r="B12" s="9">
         <v>10</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+      <c r="B13" s="9">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="2">
+      <c r="B14" s="9">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="2">
+      <c r="B15" s="9">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="2">
+      <c r="B16" s="9">
         <v>14</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="13" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
+      <c r="B17" s="9">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
+      <c r="B18" s="9">
         <v>16</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="13" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
+      <c r="B19" s="9">
         <v>17</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="13" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
+      <c r="B20" s="9">
         <v>18</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="13" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
+      <c r="B21" s="9">
         <v>19</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
+      <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
+      <c r="B23" s="9">
         <v>21</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="13" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" s="2">
+      <c r="B24" s="9">
         <v>22</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="13" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="2">
+      <c r="B25" s="9">
         <v>23</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="13" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="2">
+      <c r="B26" s="9">
         <v>24</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
+      <c r="B27" s="9">
         <v>25</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="13" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="2">
+      <c r="B28" s="9">
         <v>26</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="13" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="2">
+      <c r="B29" s="9">
         <v>27</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="13" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="2">
+      <c r="B30" s="9">
         <v>28</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="13" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="2">
+      <c r="B31" s="9">
         <v>29</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="13" t="s">
         <v>60</v>
       </c>
     </row>
